--- a/management_forms/027_fulfillment_error_reduction_pilot_application--management_forms.xlsx
+++ b/management_forms/027_fulfillment_error_reduction_pilot_application--management_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,11 +437,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>form_1</t>
+          <t>first_name</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>first_name</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>form_2</t>
+          <t>last_name</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,63 +561,63 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>form_3</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>form_4</t>
+          <t>description</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>terms_and_conditions</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>form_5</t>
+          <t>terms_and_conditions</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>consent</t>
+          <t>Terms and Conditions</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>form_6</t>
+          <t>consent</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>date_of_birth</t>
+          <t>Consent</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>form_7</t>
+          <t>date_of_birth</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>time_of_application</t>
+          <t>Date of Birth</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,41 +681,41 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>form_8</t>
+          <t>time_of_application</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>time_of_completion</t>
+          <t>Time of Application</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>form_9</t>
+          <t>time_of_completion</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>contact_address</t>
+          <t>Time of Completion</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>form_10</t>
+          <t>contact_address</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>phone_number</t>
+          <t>Contact Address</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>form_11</t>
+          <t>phone_number</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>Phone Number</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,17 +768,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>form_12</t>
+          <t>time_of_submission</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>file</t>
+          <t>Time of Submission</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,17 +791,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>form_13</t>
+          <t>submitter</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>terms_of_service</t>
+          <t>Submitter</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -814,17 +814,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>form_14</t>
+          <t>time_zone</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>date_of_submission</t>
+          <t>Time Zone</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>form_15</t>
+          <t>time_zone_offset</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>time_of_submission</t>
+          <t>Time Zone Offset</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>form_16</t>
+          <t>time_zone_name</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>submitter</t>
+          <t>Time Zone Name</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -888,18 +888,18 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>form_17</t>
+          <t>time_zone_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>time_zone</t>
+          <t>Time Zone 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>form_18</t>
+          <t>time_zone_name_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>time_zone</t>
+          <t>Time Zone Name 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -934,18 +934,18 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>form_19</t>
+          <t>time_zone_offset_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>time_zone_offset</t>
+          <t>Time Zone Offset 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -957,131 +957,16 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>form_20</t>
+          <t>submitter_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>time_zone_name</t>
+          <t>Submitter 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>form_21</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>time_zone_offset</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>form_22</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>time_zone_name</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>form_23</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>time_zone_offset</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>form_24</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>submitter</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>form_25</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -1098,12 +983,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,119 +1011,68 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>form_4_choices</t>
+          <t>terms_and_conditions_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>form_4_choices</t>
+          <t>terms_and_conditions_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>form_5_choices</t>
+          <t>consent_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>i_understand_and_agree_to_the_terms_and_conditions</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>I understand and agree to the terms and conditions</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>form_5_choices</t>
+          <t>consent_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>i_do_not_understand_and_do_not_agree_to_the_terms_and_conditions</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option_2</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>form_5_choices</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>option_3</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>option_3</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>form_13_choices</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>form_13_choices</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>I do not understand and do not agree to the terms and conditions</t>
         </is>
       </c>
     </row>
